--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -505,6 +505,34 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>(33.4k) foldable</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>$383.63</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -533,6 +533,34 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>(43.9k) compact</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>$42.05</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,34 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>trellis waterproof</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>$29.51</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,34 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>(110.8k) adjustable</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>$64.56</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -617,6 +617,34 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>(489) bundle</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>$58.08</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -645,6 +645,34 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>(33k) foldable</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>$77.26</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -673,6 +673,34 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>(11.1k) waterproof</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>$33.19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -701,6 +701,34 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>trellis portable</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>$27.35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -729,6 +729,34 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>estes tarver</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>$136.89</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -757,6 +757,34 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>micah spayer</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>$106.93</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -785,6 +785,34 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>benodin, lesley</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>$34.56</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -813,6 +813,34 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>battery lawn edger</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>$116.72</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -841,6 +841,34 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>montessori toy adjustable</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$59.03</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>68.1%</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -869,6 +869,34 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>face mask rechargeable</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$72.81</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54.2%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -897,6 +897,34 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>pegboard organizer collapsible</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>$38.70</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -925,6 +925,34 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>outdoor planter adjustable</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>$50.21</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -953,6 +953,34 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>bird bath rechargeable</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>$30.02</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>43.2%</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -981,6 +981,34 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger foldable</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>$84.68</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1009,6 +1009,34 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>battery grip bundle</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>$97.87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1037,6 +1037,34 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>cat bed adjustable</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>$35.26</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1065,6 +1065,34 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>baking sheet rechargeable</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>$62.40</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1093,6 +1093,34 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>garden hose rechargeable</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>$47.09</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>40.7%</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1121,6 +1121,34 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>sprinkler odor resistant</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>$64.00</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>42.1%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1149,6 +1149,34 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger waterproof</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>$59.68</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1177,6 +1177,34 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>trellis under $50</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>$24.00</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>40.4%</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1205,6 +1205,34 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>skincare device for apartment</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>$108.56</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1233,6 +1233,34 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>survival kit wall mounted</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>$51.01</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>42.5%</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1261,6 +1261,34 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>pegboard organizer for seniors</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>$43.39</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1289,6 +1289,34 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>skincare device hsa eligible</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>$128.39</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1317,6 +1317,34 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>speaker stand non slip</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>$46.22</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1345,6 +1345,34 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>outdoor planter for kids</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>$44.58</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>44.8%</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1373,6 +1373,34 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>massage gun accessory foldable</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>$44.67</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>40.5%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1401,6 +1401,34 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>treadmill accessory heavy duty</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>$41.13</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1429,6 +1429,34 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>charging station extra large</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>$48.33</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1457,6 +1457,34 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>speaker stand odor resistant</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>$63.08</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1485,6 +1485,34 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>raised garden bed adjustable</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>$66.60</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1513,6 +1513,34 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>raised garden bed bundle</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>$61.73</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>69.5%</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1541,6 +1541,34 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>monitor arm extra large</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>$94.19</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>68.4%</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-12.xlsx
+++ b/output/amazon_niche_rapor_2026-04-12.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1569,6 +1569,34 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>book stand gift set</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>$37.46</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
